--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N25_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0001T0006Z000C1N25_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.27573103691375</v>
+        <v>8.982306293498485</v>
       </c>
       <c r="D2" t="n">
-        <v>55.24385644522473</v>
+        <v>8.977126672349019</v>
       </c>
       <c r="E2" t="n">
-        <v>5.572238105973334</v>
+        <v>0.9054886922206667</v>
       </c>
       <c r="F2" t="n">
-        <v>5.544801023151855</v>
+        <v>0.9010301662621765</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68.82936873563882</v>
+        <v>11.18477241954131</v>
       </c>
       <c r="D3" t="n">
-        <v>68.76083131151734</v>
+        <v>11.17363508812157</v>
       </c>
       <c r="E3" t="n">
-        <v>5.572238105973334</v>
+        <v>0.9054886922206667</v>
       </c>
       <c r="F3" t="n">
-        <v>5.544801023151855</v>
+        <v>0.9010301662621765</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.6566818258029</v>
+        <v>9.856710796692971</v>
       </c>
       <c r="D4" t="n">
-        <v>60.8533331793056</v>
+        <v>9.88866664163716</v>
       </c>
       <c r="E4" t="n">
-        <v>5.572238105973334</v>
+        <v>0.9054886922206667</v>
       </c>
       <c r="F4" t="n">
-        <v>5.544801023151855</v>
+        <v>0.9010301662621765</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
